--- a/template/THV_MAU_R1_PhanLoai-KichBan.xlsx
+++ b/template/THV_MAU_R1_PhanLoai-KichBan.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tổng quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chú giải ký hiệu" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Khung 5 bước B1-B5" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Quy trình 12 HT" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Nhịp chăm sóc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cờ đỏ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tổng quan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chú giải ký hiệu" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Khung 5 bước B1-B5" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quy trình 12 HT" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Nhịp chăm sóc" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,7 +51,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0016222E"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -61,7 +62,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="0016222E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -80,6 +81,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="000B3B63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9D5D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F2F9"/>
       </patternFill>
     </fill>
@@ -91,21 +107,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DFF3E3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000B3B63"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9D5D5"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,41 +169,44 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -585,7 +589,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ — ĐỌC TRƯỚC MỌI SHEET KHÁC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ca mang dấu hiệu cần bác sĩ đánh giá sớm. Có ca bị trấn an sai thì việc đầu tiên là gọi lại khách đó hôm nay, không phải đọc tiếp báo cáo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ — đọc trước mọi con số khác</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>STT HT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Tên KH</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Mã CĐ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Dấu hiệu</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Có SĐT</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Phụ trách</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>NV có trấn an sai?</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>L-code</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Việc phải làm ngay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Phạm Văn Đức</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CĐ-1</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Xuất huyết tiêu hóa</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Phạm Linh</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CÓ: không sao đâu, chắc không sao, theo dõi thêm đã</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>L2.1</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>GỌI LẠI NGAY + rà soát lại hội thoại với trưởng nhóm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thị Hồng</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CĐ-6</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Tiền sử gia đình ung thư tiêu hóa</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thu</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>L4.1</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Lý Thị Oanh</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CĐ-2</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Sụt cân nhanh không rõ lý do</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Ngô Hà</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>L4.1</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Tỷ lệ xử lý đúng: 2/3 ca. MỐC LÀ 100% — đây là mốc duy nhất của hệ này không thương lượng. Dưới 100% thì xử lý trước khi hết kỳ, không chờ báo cáo sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Script quét bằng từ khoá và nhận RỘNG: thà gắn thừa còn hơn bỏ sót. Danh sách này CẦN NGƯỜI ĐỌC LẠI. Lưu ý máu ĐỎ TƯƠI khi đi ngoài là TH-06, không phải cờ đỏ; PHÂN ĐEN thì là cờ đỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Script quét bằng từ khoá nên chỉ gợi ý. Người đọc lại từng ca mới là nguồn chốt — đặc biệt với ca nhân viên CÓ nhận ra nhưng xử lý nửa vời.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -593,10 +855,8 @@
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="53" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="54" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -624,59 +884,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>① ĐỐI TƯỢNG</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>② NHÓM</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>③ KỊCH BẢN</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>④ NỘI DUNG</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Khách là ai, đang bị gì</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Xếp vào nhóm chăm nào</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>Chọn mã kịch bản</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Soạn tin gửi được ngay</t>
         </is>
@@ -686,375 +946,276 @@
       <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>🚩 CỜ ĐỎ — đọc trước mọi con số khác</t>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>3 ca có dấu hiệu cần khám sớm, trong đó 1 ca bị nhân viên trấn an sai. Chi tiết ở sheet "Cờ đỏ" — đọc sheet đó trước sheet này.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>STT HT</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Tên KH</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Mã CĐ</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Dấu hiệu</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Có SĐT</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Phụ trách</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>NV có trấn an sai?</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>L-code</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>Việc phải làm ngay</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Phạm Văn Đức</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>CĐ-1</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Xuất huyết tiêu hóa</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Phạm Linh</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>CÓ: không sao đâu, chắc không sao, theo dõi thêm đã</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>L2.1</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>GỌI LẠI NGAY + rà soát lại hội thoại với trưởng nhóm</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Trần Thị Hồng</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>CĐ-6</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Tiền sử gia đình ung thư tiêu hóa</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Trần Thu</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>L4.1</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>⚠ CẢNH BÁO PHƯƠNG PHÁP — đọc trước khi dùng số</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Lý Thị Oanh</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>CĐ-2</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Sụt cân nhanh không rõ lý do</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>Ngô Hà</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>L4.1</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Gọi trong SLA ≤5' + chuyển bác sĩ trong ngày</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>• Mẫu: 12 hội thoại. ⚠ Người lập báo cáo phải xác nhận đây là TOÀN BỘ hội thoại trong kỳ, hay đã lọc (theo độ dài / theo có số điện thoại).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>• 7 nhóm vấn đề có dưới 10 hội thoại → ⚠ chưa đủ mẫu, không xếp hạng, không khuyến nghị.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Tỷ lệ xử lý đúng: 2/3 ca. MỐC LÀ 100% — đây là mốc duy nhất của hệ này không thương lượng. Dưới 100% thì xử lý trước khi hết kỳ, không chờ báo cáo sau.</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• 🚩 3 ca có dấu hiệu CỜ ĐỎ trong kỳ. Luật ghi đè đẩy mọi ca này lên HOT, nên % HOT của bảng chia nhóm KHÔNG nói về chất lượng quảng cáo — đọc cột đã trừ cờ đỏ, và tách TH-01 ra khỏi mọi so sánh.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>⚠ Script quét bằng từ khoá và nhận RỘNG: thà gắn thừa còn hơn bỏ sót. Danh sách này CẦN NGƯỜI ĐỌC LẠI. Lưu ý máu ĐỎ TƯƠI khi đi ngoài là TH-06, không phải cờ đỏ; PHÂN ĐEN thì là cờ đỏ.</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• 🚩 Danh sách cờ đỏ do script quét bằng TỪ KHOÁ và nhận RỘNG. Đây là danh sách CẦN NGƯỜI ĐỌC LẠI, không phải kết luận y khoa.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• Mọi con số giá/ưu đãi trong file đều phải đối chiếu P7 bản hiện hành. Số nào trích từ hội thoại thì là 'nhân viên đã nói với khách', không phải giá chính thức. Giá của THV thay đổi theo NGƯỜI THỰC HIỆN và theo có tiền mê hay không.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>• Phễu có BA con số ở cuối: đặt lịch → đến khám → SOI ĐƯỢC. Chưa có số thì ghi ⚠ chưa đo được. Không lấy 'đặt lịch' thay cho 'đến khám', không lấy 'đến khám' thay cho 'soi được'.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>⚠ CẢNH BÁO PHƯƠNG PHÁP — đọc trước khi dùng số</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>• Mẫu: 12 hội thoại. ⚠ Người lập báo cáo phải xác nhận đây là TOÀN BỘ hội thoại trong kỳ, hay đã lọc (theo độ dài / theo có số điện thoại).</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Năm tín hiệu chấm độ nóng</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>• 7 nhóm vấn đề có dưới 10 hội thoại → ⚠ chưa đủ mẫu, không xếp hạng, không khuyến nghị.</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Tín hiệu</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Tính là CÓ khi</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>• 🚩 3 ca có dấu hiệu CỜ ĐỎ trong kỳ. Luật ghi đè đẩy mọi ca này lên HOT, nên % HOT của bảng chia nhóm KHÔNG nói về chất lượng quảng cáo — đọc cột đã trừ cờ đỏ, và tách TH-01 ra khỏi mọi so sánh.</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Nêu triệu chứng / chỉ định cụ thể</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>"đau thượng vị 2 tháng", "đi ngoài ra máu", "bác sĩ bảo cần soi đại tràng" — không tính "khám tiêu hóa"</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• 🚩 Danh sách cờ đỏ do script quét bằng TỪ KHOÁ và nhận RỘNG. Đây là danh sách CẦN NGƯỜI ĐỌC LẠI, không phải kết luận y khoa.</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Mốc thời gian ≤ 14 ngày</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>hôm nay / mai / tuần này / Chủ nhật này · đã đặt lịch · đang đến</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>• Mọi con số giá/ưu đãi trong file đều phải đối chiếu P7 bản hiện hành. Số nào trích từ hội thoại thì là 'nhân viên đã nói với khách', không phải giá chính thức. Giá của THV thay đổi theo NGƯỜI THỰC HIỆN và theo có tiền mê hay không.</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Hỏi lịch, bác sĩ, giá hoặc cách chuẩn bị theo tình trạng của mình</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>"ca của em soi loại nào", "em huyết áp cao thì mê được không" — không tính câu hỏi giá chung chung ở tin đầu</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>• Phễu có BA con số ở cuối: đặt lịch → đến khám → SOI ĐƯỢC. Chưa có số thì ghi ⚠ chưa đo được. Không lấy 'đặt lịch' thay cho 'đến khám', không lấy 'đến khám' thay cho 'soi được'.</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Gửi kết quả cũ / mô tả rõ</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>có ảnh kết quả, đơn thuốc, phiếu hẹn · hoặc mô tả đủ: triệu chứng · bao lâu · đã khám hay uống thuốc gì</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Để lại SĐT/Zalo và đồng ý nhận tư vấn</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ưu tiên có nêu khung giờ tiện nghe máy</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Năm tín hiệu chấm độ nóng</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Bốn luật ghi đè — đặc thù ngành tiêu hóa, áp bất kể điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Tín hiệu</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Tính là CÓ khi</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Luật</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Vì sao</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Nêu triệu chứng / chỉ định cụ thể</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>"đau thượng vị 2 tháng", "đi ngoài ra máu", "bác sĩ bảo cần soi đại tràng" — không tính "khám tiêu hóa"</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Đã đặt lịch / đang đến → HOT</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Hiển nhiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Mốc thời gian ≤ 14 ngày</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>hôm nay / mai / tuần này / Chủ nhật này · đã đặt lịch · đang đến</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>🚩 CÓ CỜ ĐỎ → HOT, và gắn cờ ưu tiên y tế</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ĐÂY LÀ LUẬT AN TOÀN, không phải luật bán hàng: nó tồn tại để ca này được gọi trước mọi ca khác và được chuyển bác sĩ trong ngày, không phải để nói ca này dễ chốt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Hỏi lịch, bác sĩ, giá hoặc cách chuẩn bị theo tình trạng của mình</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>"ca của em soi loại nào", "em huyết áp cao thì mê được không" — không tính câu hỏi giá chung chung ở tin đầu</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>ĐÃ CÓ KẾT QUẢ nơi khác, hoặc đã được chỉ định soi (TH-11) → HOT</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Khách đã qua giai đoạn 'có cần soi hay không', chỉ còn chọn nơi làm. Lead nóng nhất của ngành, mà tin nhắn thường rất ngắn nên bị chấm thấp oan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>④</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Gửi kết quả cũ / mô tả rõ</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>có ảnh kết quả, đơn thuốc, phiếu hẹn · hoặc mô tả đủ: triệu chứng · bao lâu · đã khám hay uống thuốc gì</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Để lại SĐT/Zalo và đồng ý nhận tư vấn</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>ưu tiên có nêu khung giờ tiện nghe máy</t>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Đến hẹn soi lại (TH-02) → tối thiểu WARM</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Nhóm này viết tin ngắn, không có triệu chứng cấp, nhưng gần như chắc chắn soi — họ chỉ đang chọn đặt lịch ở đâu</t>
         </is>
       </c>
     </row>
@@ -1064,980 +1225,885 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Bốn luật ghi đè — đặc thù ngành tiêu hóa, áp bất kể điểm</t>
+          <t>Kết quả phân loại — đếm thật từ dữ liệu</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Luật</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>Vì sao</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>Đã đặt lịch / đang đến → HOT</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Hiển nhiên</t>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Tổng hội thoại</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>🚩 CÓ CỜ ĐỎ → HOT, và gắn cờ ưu tiên y tế</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>ĐÂY LÀ LUẬT AN TOÀN, không phải luật bán hàng: nó tồn tại để ca này được gọi trước mọi ca khác và được chuyển bác sĩ trong ngày, không phải để nói ca này dễ chốt</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Có SĐT</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>ĐÃ CÓ KẾT QUẢ nơi khác, hoặc đã được chỉ định soi (TH-11) → HOT</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Khách đã qua giai đoạn 'có cần soi hay không', chỉ còn chọn nơi làm. Lead nóng nhất của ngành, mà tin nhắn thường rất ngắn nên bị chấm thấp oan</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Không có SĐT</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Đến hẹn soi lại (TH-02) → tối thiểu WARM</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>Nhóm này viết tin ngắn, không có triệu chứng cấp, nhưng gần như chắc chắn soi — họ chỉ đang chọn đặt lịch ở đâu</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Độ nóng</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả phân loại — đếm thật từ dữ liệu</t>
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>trong đó 6 ca do luật ghi đè</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>Chỉ số</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>COLD</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ghi đè: đã đặt lịch</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ghi đè: 🚩 cờ đỏ</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ghi đè: đã có kết quả nơi khác</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ghi đè: đến hẹn soi lại</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm giá trị</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Số</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Tổng hội thoại</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Có SĐT</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="n">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Nghĩa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>Combo dạ dày + đại tràng · can thiệp (cắt polyp, cầm máu) · gói tầm soát</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>41,7%</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Không có SĐT</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>58,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Độ nóng</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
-        <is>
-          <t>HOT</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>trong đó 6 ca do luật ghi đè</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>WARM</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>COLD</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: đã đặt lịch</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n">
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Soi dạ dày HOẶC đại tràng đơn lẻ · soi + test HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Khám chuyên khoa · trực tràng · sigma · siêu âm · test HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: 🚩 cờ đỏ</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: đã có kết quả nơi khác</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Chưa xác định được — thường là TH-12 hỏi chung</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ghi đè: đến hẹn soi lại</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr"/>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Lưu ý khi đọc</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr"/>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Một lead WARM của combo tầm soát (WARM·G1) đáng đầu tư hơn một lead HOT của khám đầy hơi (HOT·G3) — dải giá chênh gần chín lần. Không xếp hạng lead chỉ bằng độ nóng.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm giá trị</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm vấn đề</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Tên nhóm</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Số</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Nghĩa</t>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Đủ mẫu?</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="n">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>TH-01</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>TH-02</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>Theo dõi sau can thiệp · đến hẹn soi lại</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>TH-04</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>Dạ dày – thực quản</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>TH-05</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>Đại tràng – trực tràng</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="23" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>TH-06</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>Chảy máu thấp · trĩ – hậu môn</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>TH-09</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>Rối loạn tiêu hóa chung</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>TH-12</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>Chưa rõ / hỏi chung</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>⚠ chưa đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="20" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
-        <is>
-          <t>Combo dạ dày + đại tràng · can thiệp (cắt polyp, cầm máu) · gói tầm soát</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="n">
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>41,7%</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>Soi dạ dày HOẶC đại tràng đơn lẻ · soi + test HP</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="21" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B59" s="21" t="n">
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="21" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>16,7%</t>
         </is>
       </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>Khám chuyên khoa · trực tràng · sigma · siêu âm · test HP</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="n">
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Rào cản</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Số lượt</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>% trên tổng HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>L6.7 Ngại tiền mê / gây mê</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>SỢ</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>L6.5 Sợ nội soi</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>SỢ</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>L6.9 Ngờ vệ sinh dây soi</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>NGỜ</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>Chưa xác định được — thường là TH-12 hỏi chung</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>⚠ Lưu ý khi đọc</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="inlineStr"/>
-      <c r="C61" s="15" t="inlineStr"/>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>Một lead WARM của combo tầm soát (WARM·G1) đáng đầu tư hơn một lead HOT của khám đầy hơi (HOT·G3) — dải giá chênh gần chín lần. Không xếp hạng lead chỉ bằng độ nóng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm vấn đề</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>Tên nhóm</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>Đủ mẫu?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="22" t="inlineStr">
-        <is>
-          <t>TH-01</t>
-        </is>
-      </c>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
-        </is>
-      </c>
-      <c r="C64" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D64" s="22" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="22" t="inlineStr">
-        <is>
-          <t>TH-02</t>
-        </is>
-      </c>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>Theo dõi sau can thiệp · đến hẹn soi lại</t>
-        </is>
-      </c>
-      <c r="C65" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" s="22" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="22" t="inlineStr">
-        <is>
-          <t>TH-04</t>
-        </is>
-      </c>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>Dạ dày – thực quản</t>
-        </is>
-      </c>
-      <c r="C66" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="22" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="22" t="inlineStr">
-        <is>
-          <t>TH-05</t>
-        </is>
-      </c>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Đại tràng – trực tràng</t>
-        </is>
-      </c>
-      <c r="C67" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D67" s="22" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="22" t="inlineStr">
-        <is>
-          <t>TH-06</t>
-        </is>
-      </c>
-      <c r="B68" s="22" t="inlineStr">
-        <is>
-          <t>Chảy máu thấp · trĩ – hậu môn</t>
-        </is>
-      </c>
-      <c r="C68" s="22" t="n">
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>L6.8 Né kết quả</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>NÉ</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="22" t="inlineStr">
-        <is>
-          <t>TH-09</t>
-        </is>
-      </c>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>Rối loạn tiêu hóa chung</t>
-        </is>
-      </c>
-      <c r="C69" s="22" t="n">
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>L6.3 Chưa tài chính / hỏi bảo hiểm</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>NGẠI</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D69" s="22" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="22" t="inlineStr">
-        <is>
-          <t>TH-12</t>
-        </is>
-      </c>
-      <c r="B70" s="22" t="inlineStr">
-        <is>
-          <t>Chưa rõ / hỏi chung</t>
-        </is>
-      </c>
-      <c r="C70" s="22" t="n">
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>L6.6 Hỏi ý kiến người thân</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>NGỜ+NGẠI</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>⚠ chưa đủ mẫu</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>Giai đoạn</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>Tỷ lệ</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="15" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B74" s="15" t="n">
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>L6.2 So sánh nơi khác</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>NGỜ</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="15" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>41,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>Rào cản</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>Nhóm</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>Số lượt</t>
-        </is>
-      </c>
-      <c r="D78" s="13" t="inlineStr">
-        <is>
-          <t>% trên tổng HT</t>
-        </is>
-      </c>
-    </row>
     <row r="79">
-      <c r="A79" s="15" t="inlineStr">
-        <is>
-          <t>L6.7 Ngại tiền mê / gây mê</t>
-        </is>
-      </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>SỢ</t>
-        </is>
-      </c>
-      <c r="C79" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>25,0%</t>
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>⚠ Cách đếm</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr"/>
+      <c r="C79" s="6" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Một hội thoại có thể mang nhiều rào cản → tổng lượt LỚN HƠN tổng hội thoại là đúng, không phải lỗi.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="15" t="inlineStr">
-        <is>
-          <t>L6.5 Sợ nội soi</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>SỢ</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>L6.9 Ngờ vệ sinh dây soi</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>NGỜ</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Bảy nguyên tắc bắt buộc khi dùng nội dung trong file này</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="15" t="inlineStr">
-        <is>
-          <t>L6.8 Né kết quả</t>
-        </is>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>NÉ</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Mọi nội dung là BẢN ĐỀ XUẤT — người duyệt trước khi gửi khách.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="15" t="inlineStr">
-        <is>
-          <t>L6.3 Chưa tài chính / hỏi bảo hiểm</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="inlineStr">
-        <is>
-          <t>NGẠI</t>
-        </is>
-      </c>
-      <c r="C83" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Cột nội dung là KHUNG theo rào cản, phải cá nhân hoá theo tình trạng của chính khách đó (triệu chứng gì, bao lâu, điều khách vừa lo).</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="inlineStr">
-        <is>
-          <t>L6.6 Hỏi ý kiến người thân</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>NGỜ+NGẠI</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>🚩 Ca có CỜ ĐỎ: chỉ mời khám sớm + ghi rõ đã chuyển bác sĩ. ⛔ Không nêu giá, ⛔ không trấn an, ⛔ không nói khả năng mắc bệnh gì.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="15" t="inlineStr">
-        <is>
-          <t>L6.2 So sánh nơi khác</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>NGỜ</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>8,3%</t>
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>⛔ Không chẩn đoán, không loại trừ bệnh, không đọc kết quả xét nghiệm, không tư vấn thuốc hay phác đồ — kể cả phác đồ diệt HP.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>⚠ Cách đếm</t>
-        </is>
-      </c>
-      <c r="B86" s="15" t="inlineStr"/>
-      <c r="C86" s="15" t="inlineStr"/>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>Một hội thoại có thể mang nhiều rào cản → tổng lượt LỚN HƠN tổng hội thoại là đúng, không phải lỗi.</t>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Không dùng từ cấm: khỏi 100% · không đau · an toàn tuyệt đối · sạch HP 100% · chắc chắn không phải ung thư · tốt nhất · rẻ nhất.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Nêu khung giá công khai thì được, nhưng phải kèm BA ĐIỀU KIỆN: ai thực hiện · có tiền mê hay không · phụ phí chỉ khi có chỉ định. Chốt số cuối cho ca cụ thể thì không.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Bảy nguyên tắc bắt buộc khi dùng nội dung trong file này</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>Mọi nội dung là BẢN ĐỀ XUẤT — người duyệt trước khi gửi khách.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="15" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t>Cột nội dung là KHUNG theo rào cản, phải cá nhân hoá theo tình trạng của chính khách đó (triệu chứng gì, bao lâu, điều khách vừa lo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>🚩 Ca có CỜ ĐỎ: chỉ mời khám sớm + ghi rõ đã chuyển bác sĩ. ⛔ Không nêu giá, ⛔ không trấn an, ⛔ không nói khả năng mắc bệnh gì.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t>⛔ Không chẩn đoán, không loại trừ bệnh, không đọc kết quả xét nghiệm, không tư vấn thuốc hay phác đồ — kể cả phác đồ diệt HP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t>5.</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>Không dùng từ cấm: khỏi 100% · không đau · an toàn tuyệt đối · sạch HP 100% · chắc chắn không phải ung thư · tốt nhất · rẻ nhất.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>Nêu khung giá công khai thì được, nhưng phải kèm BA ĐIỀU KIỆN: ai thực hiện · có tiền mê hay không · phụ phí chỉ khi có chỉ định. Chốt số cuối cho ca cụ thể thì không.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>7.</t>
         </is>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>CTA là ĐẾN KHÁM với bác sĩ tiêu hóa, nói rõ bác sĩ xem xong mới quyết định có soi và soi loại nào. MỜI KHÁM LÀ PHẢI DẶN CHUẨN BỊ.</t>
         </is>
@@ -2048,7 +2114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2080,425 +2146,425 @@
       <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Ký hiệu</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Nghĩa là gì</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Dùng ở đâu</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>🚩 CĐ-1 … CĐ-6</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>CỜ ĐỎ — dấu hiệu cần bác sĩ đánh giá sớm. CĐ-1 nôn ra máu/phân đen · CĐ-2 sụt cân nhanh không rõ lý do · CĐ-3 khó nuốt tăng dần · CĐ-4 thiếu máu không rõ nguyên nhân · CĐ-5 đau bụng dữ dội liên tục/khối ở bụng/vàng da · CĐ-6 tiền sử gia đình ung thư dạ dày–đại tràng trực hệ. ĐÂY LÀ CỘT AN TOÀN, KHÔNG PHẢI CỘT BÁN HÀNG: có cờ là gọi ngay và chuyển bác sĩ trong ngày, bất kể độ nóng hay nhóm giá trị. Dòng có cờ đỏ tô đỏ đậm.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cột 🚩 Cờ đỏ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Số/thông tin CHƯA XÁC MINH. Mọi ô có ký hiệu này đều nền vàng. Không dùng để ra quyết định trước khi xác minh với THV.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Mọi sheet</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>HOT / WARM / COLD</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Mức sẵn sàng, chấm theo 5 tín hiệu. HOT 4–5 điểm · WARM 2–3 · COLD 0–1.</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Cột Độ nóng</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>① ② ③ ④ ⑤</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Năm tín hiệu: ① nêu triệu chứng/chỉ định cụ thể · ② mốc thời gian ≤14 ngày · ③ hỏi lịch/bác sĩ/giá/cách chuẩn bị theo tình trạng của mình · ④ gửi kết quả cũ hoặc mô tả rõ (triệu chứng · bao lâu · đã khám gì) · ⑤ để lại SĐT/Zalo và đồng ý nhận tư vấn.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Cột Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>[10110]</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Bitmask 5 chữ số — tín hiệu nào có, tín hiệu nào không. Ví dụ [10110] = có ①③④, thiếu ②⑤. Không có bitmask thì không ai kiểm lại được điểm.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Cột Ghi chú</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Ghi đè</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Bốn luật riêng ngành tiêu hóa, áp bất kể điểm: ① đã đặt lịch/đang đến → HOT · ② 🚩 CÓ CỜ ĐỎ → HOT (luật an toàn) · ③ ĐÃ CÓ KẾT QUẢ từ nơi khác hoặc đã được chỉ định soi (TH-11) → HOT · ④ đến hẹn soi lại (TH-02) → tối thiểu WARM.</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Cột Ghi đè?</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>% HOT*</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Chấm lại CHỈ bằng 4 tín hiệu ②③④⑤, đạt ≥3/4 tính HOT*. Dùng khi bảng chia nhóm theo nhóm vấn đề — vì tín hiệu ① chính là 'nêu vấn đề cụ thể' nên cột % HOT bị LẶP VÒNG, không so sánh được.</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Bảng nhiệt theo nhóm vấn đề</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>% HOT (trừ cờ đỏ)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Luật ghi đè ② đẩy MỌI ca cờ đỏ lên HOT, nên % HOT thường không nói về chất lượng quảng cáo mà nói về số ca đang lo bệnh. Xếp hạng post phải dùng cột đã trừ cờ đỏ.</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Sheet phân tầng post</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>G1 / G2 / G3</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Nhóm giá trị dịch vụ. G1 lớn: combo dạ dày + đại tràng · can thiệp (cắt polyp, cầm máu) · gói tầm soát. G2 trung: soi dạ dày HOẶC đại tràng đơn lẻ · soi + test HP. G3 nhỏ/cửa vào: khám · trực tràng · sigma · siêu âm · test HP. MỘT LEAD WARM CỦA COMBO TẦM SOÁT ĐÁNG HƠN MỘT LEAD HOT CỦA KHÁM ĐẦY HƠI.</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Cột Nhóm giá trị</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>TH-01 … TH-12</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>12 nhóm vấn đề tiêu hóa, xét ưu tiên từ trên xuống, TH-01 luôn thắng: TH-01 🚩 cờ đỏ · TH-02 theo dõi sau can thiệp/đến hẹn soi lại · TH-03 tầm soát không triệu chứng · TH-04 dạ dày–thực quản · TH-05 đại tràng–trực tràng · TH-06 chảy máu thấp/trĩ–hậu môn · TH-07 polyp/khối u đã biết · TH-08 gan–mật–tụy · TH-09 rối loạn tiêu hóa chung · TH-10 nhiễm HP · TH-11 mang kết quả nơi khác đến · TH-12 chưa rõ. LƯU Ý: máu ĐỎ TƯƠI → TH-06; PHÂN ĐEN → TH-01.</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Cột Nhóm vấn đề</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>L1.1 … L6.9</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Trạng thái vận hành. L1.1 lần đầu nhắn · L2.1 đang tư vấn · L2.3 chưa phản hồi · L2.4 hẹn nhắn lại · L2.5 NGOÀI HÀ NỘI · L4.1 có SĐT + nhu cầu rõ · L5.3 gọi không bắt máy · L5.4 từ chối nghe · L5.5 hẹn gọi lại · L5.6 chỉ Zalo · L6.1 chưa rõ rào cản · L6.2 so sánh nơi khác · L6.3 tài chính · L6.4 thời gian · L6.5 SỢ NỘI SOI · L6.6 hỏi người nhà · L6.7 NGẠI TIỀN MÊ · L6.8 NÉ KẾT QUẢ · L6.9 NGỜ VỆ SINH DÂY SOI. Ba mã cuối là riêng ngành tiêu hóa.</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Cột L-code</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>SỢ / NGỜ / NGẠI / NÉ</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Bốn rào cản ngành tiêu hóa. SỢ (thủ thuật) → L6.5, L6.7 · NGỜ (chất lượng, an toàn) → L6.2, L6.9 · NGẠI (nguồn lực) → L6.3, L6.4, L2.5 · NÉ (sợ chính kết quả) → L6.8. NÉ là rào cản thứ tư, không có ở ngành thẩm mỹ – nha khoa: khách biết nên soi nhưng trì hoãn vì sợ phát hiện ra bệnh. GỬI ƯU ĐÃI CHO NHÓM NÉ LÀ ĐẨY HỌ XA THÊM. Một hội thoại có thể mang nhiều rào cản nên tổng rào cản LỚN HƠN tổng hội thoại là đúng.</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cột Rào cản</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>S1 / S2 / S3 / CS</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Giai đoạn hành trình. S1 nhận biết · S2 tìm hiểu · S3 cân nhắc &amp; nỗi sợ (★ điểm quyết định) · CS sau nội soi &amp; theo dõi.</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Cột Giai đoạn</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>B1 → B5</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Khung 5 bước tư vấn: B1 mở · B2 khám phá (5 thông tin, có sàng cờ đỏ và bệnh nền) · B3 tạo tin cậy · B4 xin số có lý do · B5 xác nhận ai gọi/số nào/mấy giờ + DẶN CHUẨN BỊ.</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Sheet Khung 5 bước</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Đến khám / Soi được</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>HAI MỐC KHÁC NHAU, không được lấy mốc trước thay mốc sau. Khách đến tận phòng khám vẫn có thể không soi được: nhịn ăn chưa đủ giờ · ruột chưa sạch · không đủ điều kiện tiền mê · không có người đưa về · đến rồi không dám soi. Đây là chỗ mất tiền nhiều nhất của ngành, và phần lớn là lỗi dặn dò.</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Sheet phễu</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>T+0 → T+7</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Nhịp chăm sau khi XIN ĐƯỢC SỐ. Có hai mốc riêng của ngành: T+48h gửi hướng dẫn chuẩn bị, T–1 ngày nhắc lại. Trần 6 lần nhắn/7 ngày.</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Sheet Nhịp chăm sóc</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>D+3 / D+7 / D+15</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Nhịp chăm khi ĐÃ TƯ VẤN mà chưa đặt lịch (L6.x). Với L6.x·G1 thì nuôi tới 90 ngày, không hạ tệp ở 30 ngày.</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Sheet Nhịp chăm sóc</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>D+7 / D+21 / D+45</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Nhịp RIÊNG cho L6.8 (né kết quả), nội dung giáo dục không ưu đãi, nuôi tới 180 ngày. Người đang sợ kết quả cần thời gian, không cần bị nhắc nhiều.</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Sheet Nhịp chăm sóc</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>⚠ chưa đủ mẫu</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Nhóm/post dưới 10 hội thoại. KHÔNG xếp hạng, KHÔNG khuyến nghị. Dòng này nền xám.</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Cột Đủ mẫu?</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>[ … ]</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Chỗ trực page tự điền theo tình huống.</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Cột nội dung</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>{ … }</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Biến lấy từ P7 bản hiện hành (bảng giá &amp; chương trình tháng). Luôn kèm ⚠.</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Cột nội dung</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Dấu phân tách nhiều mã. Ví dụ TH-04 · L6.7 · WARM · G2.</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Mọi sheet</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Bước kế tiếp.</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Mọi sheet</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Màu</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>ĐỎ ĐẬM = ca có cờ đỏ (chỉ dùng cho nghĩa này) · đỏ nhạt HOT · cam WARM · xanh dương nhạt COLD · vàng mọi ô ⚠ · xanh lá nhạt khuyến nghị tốt · xám dòng chưa đủ mẫu. Màu trong bảng nhiệt CHỈ so sánh được trong cùng một bảng.</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Mọi sheet</t>
         </is>
@@ -2509,7 +2575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2542,68 +2608,68 @@
       <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Bước</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Làm gì</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Câu mẫu</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Lưu ý</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>MỞ — chào và định danh theo đúng post khách bấm vào</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Chào anh/chị, em là [tên], tư vấn viên của Tiêu Hóa Việt. Em thấy anh/chị đang quan tâm [dịch vụ theo post]. Anh/chị đang bị [tình trạng] ở vị trí nào và bao lâu rồi ạ?</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Gọi ĐÚNG TÊN dịch vụ theo quảng cáo khách vừa bấm — không hỏi chung "anh/chị cần tư vấn gì". Phản hồi trong 2 phút.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>KHÁM PHÁ — sàng cờ đỏ TRƯỚC, rồi thu đủ 5 THÔNG TIN</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Anh/chị có dấu hiệu nào như nôn ra máu, đi ngoài phân đen, sụt cân nhanh hay nuốt nghẹn không ạ?
 Trước đây anh/chị đã khám hay soi ở đâu chưa, có kết quả không ạ?
 Anh/chị có bệnh nền hay đang dùng thuốc gì không ạ?</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>NĂM thông tin: ① triệu chứng + bao lâu · ② 🚩 CÓ DẤU HIỆU CỜ ĐỎ KHÔNG · ③ đã khám/soi ở đâu chưa, có kết quả không · ④ BỆNH NỀN &amp; THUỐC ĐANG DÙNG · ⑤ thời gian dự kiến.
 Ngành tiêu hóa cần 5, nhiều hơn ngành nha hai mục là ② và ④. Thiếu ② là bỏ sót ca cần ưu tiên y tế; thiếu ④ là hẹn tiền mê cho người chưa đủ điều kiện → khách đến rồi phải về.
@@ -2612,22 +2678,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>TẠO TIN CẬY — đưa bằng chứng ĐÚNG rào cản khách mang</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Với biểu hiện kéo dài như vậy, bác sĩ cần soi mới thấy được bề mặt niêm mạc. Ở Tiêu Hóa Việt hệ nội soi là Fujifilm VP-7000 có AI, chế độ BLI/LCI giúp bác sĩ nhìn rõ các tổn thương nhỏ; cố vấn chuyên môn là TS.BS Đỗ Anh Giang, nguyên Phó Giám đốc Trung tâm Tiêu hóa - Gan mật Bệnh viện Bạch Mai.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Gỡ ĐÚNG MỘT rào cản (SỢ / NGỜ / NGẠI / NÉ), không rải hết. Thứ tự bằng chứng: chuyên gia Bạch Mai → hệ Fujifilm + AI → giấy phép Sở Y tế → bác sĩ gây mê theo dõi riêng → bảng giá công khai.
 KHÔNG HÙ BỆNH: nói về lợi ích của việc biết sớm, không về hình phạt của việc chậm. Không hứa kết quả.</t>
@@ -2635,44 +2701,44 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>XIN SỐ — lý do phải CÓ LỢI CHO KHÁCH</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Để bác sĩ xem trước thông tin và sắp lịch đúng buổi anh/chị tiện, anh/chị cho em xin số điện thoại (có Zalo) nhé. Anh/chị tiện nghe máy khung giờ nào ạ?</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>❌ Không xin số bằng lý do "để gửi ưu đãi". Luôn hỏi kèm khung giờ. Tối đa 2 lần/hội thoại.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>XÁC NHẬN — báo trước ai gọi, số nào, lúc mấy giờ</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Em cảm ơn. Khoảng [10 phút nữa / 16h chiều nay], [tên người gọi] của Tiêu Hóa Việt sẽ gọi anh/chị từ số [hotline]. Anh/chị để ý máy giúp em nhé. Bận thì nhắn em, em dời giờ cho anh/chị.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>BỐN thứ bắt buộc: tên người sẽ gọi · số sẽ gọi đến · giờ gọi · DẶN CHUẨN BỊ. Kèm lối thoát "bận thì em dời giờ".
 B5 của ngành tiêu hóa có một mục hơn ngành nha: dặn chuẩn bị. Bỏ nó là nguyên nhân số một của việc khách đến tận nơi mà không soi được.
@@ -2685,7 +2751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2727,828 +2793,828 @@
       <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Tên khách</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>🚩 Cờ đỏ</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Nhóm vấn đề</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Triệu chứng / Nhu cầu</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Giai đoạn</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Nhóm KH (insight)</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Nhóm giá trị</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Nhóm chăm sóc</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Kịch bản (mã)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Tên kịch bản</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Nội dung gợi ý gửi ngay</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Rào cản / ghi chú</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Nguyễn Thị Mai</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr"/>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>TH-04 Dạ dày – thực quản</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>B5 đã đặt lịch — CẦN DẶN CHUẨN BỊ</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>HOT · G2</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>X1 · X6</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Xác nhận ai gọi/số nào/mấy giờ + dặn chuẩn bị</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Em cảm ơn anh/chị. Khoảng [10 phút nữa / 16h chiều nay], [tên người gọi] của Tiêu Hóa Việt sẽ gọi anh/chị từ số [hotline]. Anh/chị để ý máy giúp em nhé, bận thì nhắn em dời giờ ạ.
 Em gửi kèm hướng dẫn chuẩn bị {hướng_dẫn_chuẩn_bị} ⚠ để anh/chị soi được luôn trong buổi khám nếu bác sĩ chỉ định.</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>— chưa xác định rào cản</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Lê Văn Hùng</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr"/>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>TH-12 Chưa rõ / hỏi chung</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>A1 hỏi giá ngay chưa kể triệu chứng</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>COLD · ?</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>S1.3</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Chào mở, chưa rõ nhu cầu</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Dạ chào anh/chị, em thấy anh/chị đang quan tâm [dịch vụ theo post]. Anh/chị đang có biểu hiện gì và bị bao lâu rồi ạ?
 Anh/chị có dấu hiệu nào như nôn ra máu, đi ngoài phân đen, sụt cân nhanh hay nuốt nghẹn không ạ?
 ⚠ Khung mở hội thoại - cần cá nhân hoá theo tình trạng của chính khách này.</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>— chưa xác định rào cản</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Trần Thị Hồng</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>🚩 CĐ-6</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>TH-01 🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Z 🚩 CA CỜ ĐỎ — xử lý trước mọi nhóm</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>HOT · G1</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>X5</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>🚩 CA CỜ ĐỎ — mời khám trong ngày, chuyển bác sĩ, không nêu giá</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>Dạ [tên khách], với dấu hiệu anh/chị kể thì bác sĩ cần xem sớm ạ. Em chuyển bác sĩ của phòng khám xem trường hợp của anh/chị ngay. Anh/chị đến được trong hôm nay hay sáng mai ạ? Phòng khám mở 7h-17h cả Chủ nhật.
 ⛔ KHUNG CHO CA CỜ ĐỎ: không nêu giá · không trấn an · không nói khả năng mắc bệnh gì. Ghi rõ đã chuyển bác sĩ.</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>L6.7 Ngại tiền mê / gây mê · L6.5 Sợ nội soi</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Phạm Văn Đức</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>🚩 CĐ-1</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>TH-01 🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Z 🚩 CA CỜ ĐỎ — xử lý trước mọi nhóm</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>HOT · G1</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>X5</t>
         </is>
       </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>🚩 CA CỜ ĐỎ — mời khám trong ngày, chuyển bác sĩ, không nêu giá</t>
         </is>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Dạ [tên khách], với dấu hiệu anh/chị kể thì bác sĩ cần xem sớm ạ. Em chuyển bác sĩ của phòng khám xem trường hợp của anh/chị ngay. Anh/chị đến được trong hôm nay hay sáng mai ạ? Phòng khám mở 7h-17h cả Chủ nhật.
 ⛔ KHUNG CHO CA CỜ ĐỎ: không nêu giá · không trấn an · không nói khả năng mắc bệnh gì. Ghi rõ đã chuyển bác sĩ.</t>
         </is>
       </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>— chưa xác định rào cản</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Vũ Thị Lan</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr"/>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>TH-06 Chảy máu thấp · trĩ – hậu môn</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>A4 sợ nội soi hoặc ngại tiền mê</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>COLD · G3</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>S3.2</t>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>Ngại tiền mê — sàng lọc trước mê, bác sĩ gây mê theo dõi riêng</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>Dạ với [bệnh nền anh/chị vừa kể] thì bác sĩ phải khám sàng lọc trước mới quyết định được có tiền mê hay không, em chưa dám hứa trước ạ. Khi làm tiền mê thì có bác sĩ gây mê theo dõi riêng trong suốt ca soi.
 Anh/chị tiện [sáng mai] hay [Chủ nhật này] để bác sĩ khám và đánh giá ạ?</t>
         </is>
       </c>
-      <c r="M9" s="15" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>L6.7 Ngại tiền mê / gây mê · L6.5 Sợ nội soi</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Đỗ Minh Quân</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr"/>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>TH-02 Theo dõi sau can thiệp · đến hẹn soi lại</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>C2 đến hẹn soi lại</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>HOT · G2</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>S3.1</t>
         </is>
       </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Sợ nội soi — nói thật cảm giác, nêu bản tiền mê</t>
         </is>
       </c>
-      <c r="L10" s="15" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>Dạ em nói thật với anh/chị: soi thường có cảm giác khó chịu, không phải không có. Còn bản tiền mê thì anh/chị ngủ trong lúc soi, có bác sĩ gây mê theo dõi riêng ạ.
 Anh/chị đến khám trước đã, bác sĩ xem rồi mới quyết định có cần soi và soi loại nào. Anh/chị tiện [khung giờ 1] hay [khung giờ 2] ạ?</t>
         </is>
       </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>L6.5 Sợ nội soi · L6.9 Ngờ vệ sinh dây soi</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Hoàng Thị Thu</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr"/>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>TH-09 Rối loạn tiêu hóa chung</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>A7 né kết quả (L6.8)</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>COLD · G3</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>S3.7</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>NÉ KẾT QUẢ — nói về lợi ích biết sớm, KHÔNG gửi ưu đãi</t>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>Dạ em hiểu ạ. Phần lớn tổn thương phát hiện sớm thì xử lý được, có những tổn thương nhỏ bác sĩ xử lý ngay trong lúc soi. Biết sớm là để chủ động, anh/chị ạ.
 Em giữ giúp anh/chị buổi [Chủ nhật tuần sau] nhé, đổi được nếu anh/chị có việc.
 ⛔ KHÔNG gửi ưu đãi giảm giá cho nhóm này - họ không lùi vì tiền.</t>
         </is>
       </c>
-      <c r="M11" s="15" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>L6.8 Né kết quả</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Bùi Văn Nam</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr"/>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>TH-05 Đại tràng – trực tràng</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>A2 triệu chứng dai dẳng, đã tự uống thuốc</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>WARM · G2</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>S3.5</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>Chưa tài chính — khung giá công khai + ba điều kiện</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Dạ bảng giá bên em công khai từng mục ạ: [khung giá theo P7]. Mức cụ thể phụ thuộc ba thứ - ai thực hiện · có tiền mê hay không · sinh thiết hay cắt polyp thì chỉ phát sinh khi bác sĩ chỉ định.
 ⚠ Mọi con số lấy từ P7 bản hiện hành. Phần bảo hiểm: ⚠ chờ THV cấp.
 Anh/chị đến khám trước để biết mình cần làm gì đã nhé, tiện [khung giờ 1] hay [khung giờ 2] ạ?</t>
         </is>
       </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>L6.3 Chưa tài chính / hỏi bảo hiểm</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Nguyễn Thị Bích</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr"/>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>TH-02 Theo dõi sau can thiệp · đến hẹn soi lại</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>C2 đến hẹn soi lại</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>HOT · G1</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>S3.2</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>Ngại tiền mê — sàng lọc trước mê, bác sĩ gây mê theo dõi riêng</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>Dạ với [bệnh nền anh/chị vừa kể] thì bác sĩ phải khám sàng lọc trước mới quyết định được có tiền mê hay không, em chưa dám hứa trước ạ. Khi làm tiền mê thì có bác sĩ gây mê theo dõi riêng trong suốt ca soi.
 Anh/chị tiện [sáng mai] hay [Chủ nhật này] để bác sĩ khám và đánh giá ạ?</t>
         </is>
       </c>
-      <c r="M13" s="15" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>L6.7 Ngại tiền mê / gây mê · L6.6 Hỏi ý kiến người thân</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Trịnh Quốc Việt</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>TH-04 Dạ dày – thực quản</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>A2 triệu chứng dai dẳng, đã tự uống thuốc</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>WARM · G2</t>
         </is>
       </c>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>S3.4</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>So sánh nơi khác — đưa bộ tiêu chí, không nói xấu tuyến công</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>Dạ anh/chị so sánh là đúng ạ, và em không so sánh với bệnh viện. Em nói anh/chị mấy điểm để tự đối chiếu: ai là người trực tiếp soi và kinh nghiệm bao lâu · hệ máy đời nào, có chế độ nhuộm ảo không · có bác sĩ gây mê riêng không · bảng giá có công khai không.
 Ở bên em cố vấn chuyên môn là TS.BS Đỗ Anh Giang, nguyên Phó Giám đốc Trung tâm Tiêu hóa - Gan mật Bệnh viện Bạch Mai; hệ nội soi là Fujifilm VP-7000 có AI.
 Anh/chị tiện [khung giờ 1] hay [khung giờ 2] ạ?</t>
         </is>
       </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>L6.2 So sánh nơi khác</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Lý Thị Oanh</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>🚩 CĐ-2</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>TH-01 🚩 CỜ ĐỎ — dấu hiệu cần khám ngay</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Z 🚩 CA CỜ ĐỎ — xử lý trước mọi nhóm</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>HOT · G1</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>X5</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>🚩 CA CỜ ĐỎ — mời khám trong ngày, chuyển bác sĩ, không nêu giá</t>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>Dạ [tên khách], với dấu hiệu anh/chị kể thì bác sĩ cần xem sớm ạ. Em chuyển bác sĩ của phòng khám xem trường hợp của anh/chị ngay. Anh/chị đến được trong hôm nay hay sáng mai ạ? Phòng khám mở 7h-17h cả Chủ nhật.
 ⛔ KHUNG CHO CA CỜ ĐỎ: không nêu giá · không trấn an · không nói khả năng mắc bệnh gì. Ghi rõ đã chuyển bác sĩ.</t>
         </is>
       </c>
-      <c r="M15" s="15" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>— chưa xác định rào cản</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Phan Thanh Tùng</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr"/>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>TH-05 Đại tràng – trực tràng</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>⚠ điền từ hội thoại — triệu chứng · bao lâu · đã khám/uống thuốc gì</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>A2 triệu chứng dai dẳng, đã tự uống thuốc</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>WARM · G2</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>S1.3</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>Chào mở, chưa rõ nhu cầu</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Dạ chào anh/chị, em thấy anh/chị đang quan tâm [dịch vụ theo post]. Anh/chị đang có biểu hiện gì và bị bao lâu rồi ạ?
 Anh/chị có dấu hiệu nào như nôn ra máu, đi ngoài phân đen, sụt cân nhanh hay nuốt nghẹn không ạ?
 ⚠ Khung mở hội thoại - cần cá nhân hoá theo tình trạng của chính khách này.</t>
         </is>
       </c>
-      <c r="M16" s="15" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>— chưa xác định rào cản</t>
         </is>
@@ -3559,7 +3625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3593,378 +3659,378 @@
       <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Nhóm</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Khi nào dùng</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Nhịp chạm</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Kịch bản gợi ý</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Điều kiện dừng</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>🚩 CỜ ĐỎ</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Hội thoại có dấu hiệu CĐ-1…CĐ-6</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>GỌI NGAY bất kể độ nóng, bất kể khung giờ. SLA ≤5'. Chuyển bác sĩ trong ngày</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>X5</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Đã đến khám. ⛔ Không bao giờ 'thoát' bằng cách im lặng — khách không phản hồi thì vẫn ghi vào danh sách chưa tiếp cận được</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>HOT · G1</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Có SĐT, ca combo tầm soát / can thiệp / gói chuyên gia</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>T+0 ≤2' → T+30' → T+2h → T+24h → T+48h gửi hướng dẫn chuẩn bị → T-1 ngày nhắc lại → T+7 ngày. SLA gọi ≤10'</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>X1 → S3.x theo rào cản → X6 dặn chuẩn bị</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Đã thực hiện nội soi → chuyển luồng kết quả &amp; theo dõi</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>HOT · G2–G3</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Có SĐT, dịch vụ giá trị trung/nhỏ</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>T+0 ≤2' → T+30' → T+24h → T+48h gửi hướng dẫn chuẩn bị. SLA gọi ≤15'</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>X1 · X6</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Đã soi được, hoặc chốt lịch gọn</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>HOT gọi nhỡ</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Đã có số, gọi không bắt máy (L5.3)</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>T+30' nhắn hỏi khung giờ → T+24h gọi lần 2 (nhắn nhắc 15' trước)</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Khách phản hồi, hoặc hết trần 6 lần/7 ngày</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>ĐÃ CÓ LỊCH</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Khách đã đặt được buổi khám (B5)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>T+48h gửi hướng dẫn chuẩn bị + hỏi bệnh nền, thuốc đang dùng, có người đưa về không → T-1 ngày nhắc lại giờ nhịn ăn và mang kết quả cũ</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>X6</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Đã soi được. Đây là nhịp chặn mốc rò nặng nhất của ngành</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>WARM · G1</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Chưa sẵn sàng NHƯNG là ca giá trị lớn (gồm TH-03 tầm soát)</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>D+3 → D+7 → D+15 → sau đó 2 tuần/lần. NUÔI TỚI 90 NGÀY, không hạ tệp ở 30 ngày</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>S3.x theo rào cản + nội dung giáo dục</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Khách từ chối dứt khoát, hoặc quá 90 ngày không tiến triển</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>WARM · G2–G3</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Chưa sẵn sàng, dịch vụ giá trị trung/nhỏ</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>D+3 → D+7 → D+15</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>S3.x theo rào cản</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Quá 30 ngày không tiến triển → tệp remarketing</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>COLD</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Hỏi tham khảo, 0–1 tín hiệu</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Nuôi bằng nội dung, không chạm dồn dập</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>X4</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Quá 30 ngày → tệp remarketing</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>L6.8 NÉ KẾT QUẢ</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Biết nên soi nhưng trì hoãn vì sợ phát hiện ra bệnh</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>D+7 → D+21 → D+45, nội dung GIÁO DỤC, nhịp thưa. NUÔI TỚI 180 NGÀY</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>S3.7 — ⛔ KHÔNG gửi ưu đãi giảm giá, họ không lùi vì tiền</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Khách tự quay lại, hoặc từ chối dứt khoát. Nhóm này quay lại muộn nhưng quay lại thật — cắt ở 30 ngày là bỏ tệp dễ gọi lại nhất</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Ở xa Hà Nội (L2.5)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Ngoài Hà Nội và vùng lân cận</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Chốt một buổi gọn: khám + soi + nhận kết quả trong ngày</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>S3.9</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Khách chốt được buổi, hoặc từ chối vì khoảng cách</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>TH-11 mang kết quả nơi khác</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Đã có kết quả soi/CT/xét nghiệm</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Gọi sớm (HOT theo ghi đè ③), mời bác sĩ đọc trực tiếp</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>S4.1 — ⛔ KHÔNG đọc kết quả qua inbox, ⛔ không bình luận nơi cũ</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Đã đến khám để bác sĩ đọc kết quả</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>TH-02 đến hẹn soi lại</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Đã cắt polyp / đang theo dõi / bác sĩ hẹn</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Nhắc theo MỐC ĐÃ GHI TRONG PHIẾU KẾT QUẢ của khách</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>S4.2 — ⚠ không tự nêu số năm chu kỳ, đó là chỉ định của bác sĩ</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Đã soi lại. Tệp giá trị dài hạn lớn nhất của THV</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Người nhà đặt hộ</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Hội thoại nhắc "cho bố", "cho mẹ", "cả nhà"</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Nói với người đặt về quy trình và chuẩn bị; nói với người bệnh về cảm giác</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>CS + mời người nhà cùng tầm soát</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Nhóm này hay bị chấm COLD oan — giữ trong tệp LTV, không bỏ</t>
         </is>
@@ -3974,19 +4040,19 @@
       <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>⚠ TRẦN NHẮN</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Tối đa 6 lần nhắn / 7 ngày. Khách từ chối thì DỪNG NGAY.</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
